--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0109.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0109.xlsx
@@ -32572,7 +32572,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Cậu phải tin ta chứ! Ta còn thức đêm thức hôm làm mấy tấm poster tuyển tình nguyện viên thử nghiệm này nữa!</t>
+          <t>Cậu phải tin tao chứ! Tao còn thức đêm thức hôm làm mấy tấm poster tuyển tình nguyện viên thử nghiệm này nữa!</t>
         </is>
       </c>
     </row>
